--- a/data/historico/dados_2026-10-13.xlsx
+++ b/data/historico/dados_2026-10-13.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="73">
   <si>
     <t>data</t>
   </si>
@@ -151,16 +151,22 @@
     <t>media_ultimos_3m</t>
   </si>
   <si>
-    <t>media_3m_anteriores</t>
+    <t>media_mesmos_3m_ano_anterior</t>
   </si>
   <si>
-    <t>momentum_pct</t>
+    <t>momentum_yoy_pct</t>
   </si>
   <si>
-    <t>volatilidade</t>
+    <t>volatilidade_sem_tendencia</t>
   </si>
   <si>
     <t>status_momentum</t>
+  </si>
+  <si>
+    <t>volume_medio_escala_conjunta</t>
+  </si>
+  <si>
+    <t>baixo_volume</t>
   </si>
   <si>
     <t>Acelerando</t>
@@ -7810,10 +7816,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -7844,8 +7850,14 @@
       <c r="J1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -7865,19 +7877,25 @@
         <v>73.26666666666667</v>
       </c>
       <c r="G2">
-        <v>67.59999999999999</v>
+        <v>61.79999999999999</v>
       </c>
       <c r="H2">
-        <v>0.08382642998027623</v>
+        <v>0.1855447680690401</v>
       </c>
       <c r="I2">
-        <v>0.3652523767312169</v>
+        <v>0.3398886850033078</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>49</v>
+      </c>
+      <c r="K2">
+        <v>20.94222222222222</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -7897,19 +7915,25 @@
         <v>39.56666666666667</v>
       </c>
       <c r="G3">
-        <v>45.46666666666667</v>
+        <v>54.8</v>
       </c>
       <c r="H3">
-        <v>-0.1297653958944281</v>
+        <v>-0.2779805352798054</v>
       </c>
       <c r="I3">
-        <v>0.3074506518579602</v>
+        <v>0.274203165868446</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>50</v>
+      </c>
+      <c r="K3">
+        <v>30.81111111111111</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -7929,19 +7953,25 @@
         <v>54.96666666666667</v>
       </c>
       <c r="G4">
-        <v>62.96666666666666</v>
+        <v>60.73333333333333</v>
       </c>
       <c r="H4">
-        <v>-0.1270513499205927</v>
+        <v>-0.09495060373216235</v>
       </c>
       <c r="I4">
-        <v>0.2435781924544769</v>
+        <v>0.2384309380350671</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>50</v>
+      </c>
+      <c r="K4">
+        <v>58.80888888888889</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -7961,19 +7991,25 @@
         <v>68.53333333333332</v>
       </c>
       <c r="G5">
-        <v>57.6</v>
+        <v>65.03333333333333</v>
       </c>
       <c r="H5">
-        <v>0.1898148148148144</v>
+        <v>0.05381855458739082</v>
       </c>
       <c r="I5">
-        <v>0.4025134284295585</v>
+        <v>0.3972232719815187</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>49</v>
+      </c>
+      <c r="K5">
+        <v>8.92</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -7993,16 +8029,22 @@
         <v>62.90000000000001</v>
       </c>
       <c r="G6">
-        <v>46.83333333333334</v>
+        <v>77.63333333333333</v>
       </c>
       <c r="H6">
-        <v>0.3430604982206407</v>
+        <v>-0.1897810218978101</v>
       </c>
       <c r="I6">
-        <v>1.247590484989705</v>
+        <v>0.9108715011909452</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="K6">
+        <v>1.628888888888889</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8026,16 +8068,16 @@
         <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" t="s">
         <v>15</v>
@@ -8044,19 +8086,19 @@
         <v>16</v>
       </c>
       <c r="J1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M1" t="s">
         <v>20</v>
       </c>
       <c r="N1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -8067,40 +8109,40 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>1.038117402503502</v>
+        <v>1.070870441110096</v>
       </c>
       <c r="D2">
-        <v>0.7529147272809437</v>
+        <v>0.7632387060879151</v>
       </c>
       <c r="E2">
-        <v>0.8550996430023952</v>
+        <v>0.8886034333645982</v>
       </c>
       <c r="F2">
-        <v>0.9089882055221655</v>
+        <v>0.8606972590649574</v>
       </c>
       <c r="G2">
-        <v>0.8988205522165484</v>
+        <v>0.7043276950963847</v>
       </c>
       <c r="H2">
-        <v>1.037609019838222</v>
+        <v>0.9792467550974214</v>
       </c>
       <c r="I2">
-        <v>1.547516833114917</v>
+        <v>1.50600656111246</v>
       </c>
       <c r="J2">
-        <v>0.9893126666365404</v>
+        <v>0.9605914046171105</v>
       </c>
       <c r="K2">
-        <v>0.9476252880835105</v>
+        <v>0.9979082548121841</v>
       </c>
       <c r="L2">
-        <v>0.9442360703149716</v>
+        <v>1.027292101142923</v>
       </c>
       <c r="M2">
-        <v>0.8988205522165484</v>
+        <v>0.9670020257179713</v>
       </c>
       <c r="N2">
-        <v>1.188937593203489</v>
+        <v>1.274215362775978</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -8111,40 +8153,40 @@
         <v>28</v>
       </c>
       <c r="C3">
-        <v>1.056929839682814</v>
+        <v>1.062902256186142</v>
       </c>
       <c r="D3">
-        <v>0.7417902085847269</v>
+        <v>0.7569694334088459</v>
       </c>
       <c r="E3">
-        <v>0.8823909670746425</v>
+        <v>0.9269655070432998</v>
       </c>
       <c r="F3">
-        <v>1.047718065850716</v>
+        <v>1.058506288579985</v>
       </c>
       <c r="G3">
-        <v>0.9269953456300639</v>
+        <v>0.8250612035577399</v>
       </c>
       <c r="H3">
-        <v>1.039960782623686</v>
+        <v>1.010116324106268</v>
       </c>
       <c r="I3">
-        <v>1.31922297879676</v>
+        <v>1.326306658992809</v>
       </c>
       <c r="J3">
-        <v>0.8906330805033617</v>
+        <v>0.901371160515673</v>
       </c>
       <c r="K3">
-        <v>0.8213023616617826</v>
+        <v>0.8538312591729526</v>
       </c>
       <c r="L3">
-        <v>1.031072228926047</v>
+        <v>1.002782918955907</v>
       </c>
       <c r="M3">
-        <v>1.075676607481469</v>
+        <v>1.050246768904466</v>
       </c>
       <c r="N3">
-        <v>1.25732632304775</v>
+        <v>1.224940220575912</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -8155,40 +8197,40 @@
         <v>29</v>
       </c>
       <c r="C4">
-        <v>1.038958585247884</v>
+        <v>1.054535743129976</v>
       </c>
       <c r="D4">
-        <v>0.7830448911729141</v>
+        <v>0.7750694659227809</v>
       </c>
       <c r="E4">
-        <v>0.9539374244256349</v>
+        <v>0.9685071104470736</v>
       </c>
       <c r="F4">
-        <v>1.099748715235792</v>
+        <v>1.150512591880149</v>
       </c>
       <c r="G4">
-        <v>0.9007991989117292</v>
+        <v>0.8202870399905889</v>
       </c>
       <c r="H4">
-        <v>1.126530380894801</v>
+        <v>1.081793668137913</v>
       </c>
       <c r="I4">
-        <v>1.412201481257557</v>
+        <v>1.40732946093065</v>
       </c>
       <c r="J4">
-        <v>0.8353329050785974</v>
+        <v>0.8550062035360964</v>
       </c>
       <c r="K4">
-        <v>0.7668908706166868</v>
+        <v>0.7906223368882607</v>
       </c>
       <c r="L4">
-        <v>0.8949894195888755</v>
+        <v>0.8886381619650251</v>
       </c>
       <c r="M4">
-        <v>1.044626662636034</v>
+        <v>1.042474847319326</v>
       </c>
       <c r="N4">
-        <v>1.170457980652962</v>
+        <v>1.165223369852161</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -8199,40 +8241,40 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>1.198505191177084</v>
+        <v>1.22649143104026</v>
       </c>
       <c r="D5">
-        <v>0.8152649793603802</v>
+        <v>0.8926328497362793</v>
       </c>
       <c r="E5">
-        <v>0.996330734270108</v>
+        <v>1.06469830632306</v>
       </c>
       <c r="F5">
-        <v>0.8649876996205645</v>
+        <v>0.9211864656367723</v>
       </c>
       <c r="G5">
-        <v>0.7434953925697368</v>
+        <v>0.579558585716298</v>
       </c>
       <c r="H5">
-        <v>0.9639640578743276</v>
+        <v>0.6926643189181574</v>
       </c>
       <c r="I5">
-        <v>1.50200141767085</v>
+        <v>1.456958491016676</v>
       </c>
       <c r="J5">
-        <v>0.9620877288079055</v>
+        <v>0.9215357718629864</v>
       </c>
       <c r="K5">
-        <v>0.6773547929783597</v>
+        <v>0.6011759667310625</v>
       </c>
       <c r="L5">
-        <v>0.909394154192553</v>
+        <v>0.9670878943882227</v>
       </c>
       <c r="M5">
-        <v>1.157069590960263</v>
+        <v>1.257753962370386</v>
       </c>
       <c r="N5">
-        <v>1.301546929074761</v>
+        <v>1.41825595625984</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8243,40 +8285,40 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>0.6360864745011086</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.1938001023366877</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1.323980897151629</v>
+        <v>3.347582985793593</v>
       </c>
       <c r="F6">
-        <v>0.8989638410370118</v>
+        <v>0.9651100094932582</v>
       </c>
       <c r="G6">
-        <v>0.8625063960429813</v>
+        <v>0.4167072972533723</v>
       </c>
       <c r="H6">
-        <v>1.365235374381716</v>
+        <v>0.5408743702259061</v>
       </c>
       <c r="I6">
-        <v>1.499552276991301</v>
+        <v>0.6143344709897611</v>
       </c>
       <c r="J6">
-        <v>1.819034623912672</v>
+        <v>0.5824800910125142</v>
       </c>
       <c r="K6">
-        <v>0.726270680538973</v>
+        <v>0.3172436209978872</v>
       </c>
       <c r="L6">
-        <v>0.8481152993348113</v>
+        <v>0.4310092637737689</v>
       </c>
       <c r="M6">
-        <v>0.7879924953095685</v>
+        <v>0.4004550625711036</v>
       </c>
       <c r="N6">
-        <v>0.9299846494968446</v>
+        <v>4.384202827888835</v>
       </c>
     </row>
   </sheetData>
@@ -8297,7 +8339,7 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -8894,10 +8936,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -8917,13 +8959,16 @@
         <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>60</v>
+      </c>
+      <c r="I1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -8937,19 +8982,22 @@
         <v>0.4616716122650841</v>
       </c>
       <c r="E2">
-        <v>0.08382642998027623</v>
+        <v>0.1855447680690401</v>
       </c>
       <c r="F2">
-        <v>0.3652523767312169</v>
+        <v>0.3398886850033078</v>
       </c>
       <c r="G2">
         <v>7</v>
       </c>
       <c r="H2">
-        <v>1.547516833114917</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>1.50600656111246</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -8963,19 +9011,22 @@
         <v>-0.1498968599587441</v>
       </c>
       <c r="E3">
-        <v>-0.1297653958944281</v>
+        <v>-0.2779805352798054</v>
       </c>
       <c r="F3">
-        <v>0.3074506518579602</v>
+        <v>0.274203165868446</v>
       </c>
       <c r="G3">
         <v>7</v>
       </c>
       <c r="H3">
-        <v>1.31922297879676</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>1.326306658992809</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -8989,19 +9040,22 @@
         <v>0.01981767736821261</v>
       </c>
       <c r="E4">
-        <v>-0.1270513499205927</v>
+        <v>-0.09495060373216235</v>
       </c>
       <c r="F4">
-        <v>0.2435781924544769</v>
+        <v>0.2384309380350671</v>
       </c>
       <c r="G4">
         <v>7</v>
       </c>
       <c r="H4">
-        <v>1.412201481257557</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>1.40732946093065</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -9015,19 +9069,22 @@
         <v>-0.005250328145509076</v>
       </c>
       <c r="E5">
-        <v>0.1898148148148144</v>
+        <v>0.05381855458739082</v>
       </c>
       <c r="F5">
-        <v>0.4025134284295585</v>
+        <v>0.3972232719815187</v>
       </c>
       <c r="G5">
         <v>7</v>
       </c>
       <c r="H5">
-        <v>1.50200141767085</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>1.456958491016676</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -9041,16 +9098,19 @@
         <v>0.05183282745738982</v>
       </c>
       <c r="E6">
-        <v>0.3430604982206407</v>
+        <v>-0.1897810218978101</v>
       </c>
       <c r="F6">
-        <v>1.247590484989705</v>
+        <v>0.9108715011909452</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>1.819034623912672</v>
+        <v>4.384202827888835</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9124,7 +9184,7 @@
         <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -9156,7 +9216,7 @@
         <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -9188,7 +9248,7 @@
         <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -9220,7 +9280,7 @@
         <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -9252,7 +9312,7 @@
         <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -9284,7 +9344,7 @@
         <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -9316,7 +9376,7 @@
         <v>37</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -9348,7 +9408,7 @@
         <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -9380,7 +9440,7 @@
         <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -9412,7 +9472,7 @@
         <v>37</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -9444,7 +9504,7 @@
         <v>37</v>
       </c>
       <c r="J12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -9476,7 +9536,7 @@
         <v>37</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -9508,7 +9568,7 @@
         <v>37</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -9540,7 +9600,7 @@
         <v>37</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -9572,7 +9632,7 @@
         <v>37</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -9604,7 +9664,7 @@
         <v>37</v>
       </c>
       <c r="J17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -9636,7 +9696,7 @@
         <v>37</v>
       </c>
       <c r="J18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -9668,7 +9728,7 @@
         <v>37</v>
       </c>
       <c r="J19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -9700,7 +9760,7 @@
         <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9732,7 +9792,7 @@
         <v>37</v>
       </c>
       <c r="J21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -9764,7 +9824,7 @@
         <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -9796,7 +9856,7 @@
         <v>37</v>
       </c>
       <c r="J23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -9828,7 +9888,7 @@
         <v>37</v>
       </c>
       <c r="J24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -9860,7 +9920,7 @@
         <v>37</v>
       </c>
       <c r="J25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -9892,7 +9952,7 @@
         <v>37</v>
       </c>
       <c r="J26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -9924,7 +9984,7 @@
         <v>37</v>
       </c>
       <c r="J27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -9956,7 +10016,7 @@
         <v>37</v>
       </c>
       <c r="J28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -9988,7 +10048,7 @@
         <v>37</v>
       </c>
       <c r="J29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -10020,7 +10080,7 @@
         <v>37</v>
       </c>
       <c r="J30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -10052,7 +10112,7 @@
         <v>37</v>
       </c>
       <c r="J31" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -10084,7 +10144,7 @@
         <v>37</v>
       </c>
       <c r="J32" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -10116,7 +10176,7 @@
         <v>37</v>
       </c>
       <c r="J33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -10148,7 +10208,7 @@
         <v>37</v>
       </c>
       <c r="J34" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -10180,7 +10240,7 @@
         <v>37</v>
       </c>
       <c r="J35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -10212,7 +10272,7 @@
         <v>37</v>
       </c>
       <c r="J36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -10244,7 +10304,7 @@
         <v>37</v>
       </c>
       <c r="J37" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -10276,7 +10336,7 @@
         <v>37</v>
       </c>
       <c r="J38" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -10308,7 +10368,7 @@
         <v>37</v>
       </c>
       <c r="J39" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -10340,7 +10400,7 @@
         <v>37</v>
       </c>
       <c r="J40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -10372,7 +10432,7 @@
         <v>37</v>
       </c>
       <c r="J41" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -10404,7 +10464,7 @@
         <v>37</v>
       </c>
       <c r="J42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -10436,7 +10496,7 @@
         <v>37</v>
       </c>
       <c r="J43" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -10468,7 +10528,7 @@
         <v>37</v>
       </c>
       <c r="J44" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -10500,7 +10560,7 @@
         <v>37</v>
       </c>
       <c r="J45" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -10532,7 +10592,7 @@
         <v>37</v>
       </c>
       <c r="J46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -10564,7 +10624,7 @@
         <v>37</v>
       </c>
       <c r="J47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -10596,7 +10656,7 @@
         <v>37</v>
       </c>
       <c r="J48" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -10628,7 +10688,7 @@
         <v>37</v>
       </c>
       <c r="J49" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -10660,7 +10720,7 @@
         <v>37</v>
       </c>
       <c r="J50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -10692,7 +10752,7 @@
         <v>37</v>
       </c>
       <c r="J51" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -10724,7 +10784,7 @@
         <v>37</v>
       </c>
       <c r="J52" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -10756,7 +10816,7 @@
         <v>37</v>
       </c>
       <c r="J53" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -10788,7 +10848,7 @@
         <v>37</v>
       </c>
       <c r="J54" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -10820,7 +10880,7 @@
         <v>37</v>
       </c>
       <c r="J55" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -10852,7 +10912,7 @@
         <v>37</v>
       </c>
       <c r="J56" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -10884,7 +10944,7 @@
         <v>37</v>
       </c>
       <c r="J57" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -10916,7 +10976,7 @@
         <v>37</v>
       </c>
       <c r="J58" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -10948,7 +11008,7 @@
         <v>37</v>
       </c>
       <c r="J59" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -10980,7 +11040,7 @@
         <v>37</v>
       </c>
       <c r="J60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -11012,7 +11072,7 @@
         <v>37</v>
       </c>
       <c r="J61" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -11044,7 +11104,7 @@
         <v>37</v>
       </c>
       <c r="J62" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -11076,7 +11136,7 @@
         <v>37</v>
       </c>
       <c r="J63" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -11108,7 +11168,7 @@
         <v>37</v>
       </c>
       <c r="J64" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -11140,7 +11200,7 @@
         <v>37</v>
       </c>
       <c r="J65" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -11172,7 +11232,7 @@
         <v>37</v>
       </c>
       <c r="J66" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -11204,7 +11264,7 @@
         <v>37</v>
       </c>
       <c r="J67" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -11236,7 +11296,7 @@
         <v>37</v>
       </c>
       <c r="J68" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -11268,7 +11328,7 @@
         <v>37</v>
       </c>
       <c r="J69" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -11300,7 +11360,7 @@
         <v>37</v>
       </c>
       <c r="J70" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -11332,7 +11392,7 @@
         <v>37</v>
       </c>
       <c r="J71" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -11364,7 +11424,7 @@
         <v>37</v>
       </c>
       <c r="J72" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -11396,7 +11456,7 @@
         <v>37</v>
       </c>
       <c r="J73" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -11428,7 +11488,7 @@
         <v>37</v>
       </c>
       <c r="J74" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -11460,7 +11520,7 @@
         <v>37</v>
       </c>
       <c r="J75" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -11492,7 +11552,7 @@
         <v>37</v>
       </c>
       <c r="J76" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -11524,7 +11584,7 @@
         <v>37</v>
       </c>
       <c r="J77" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -11556,7 +11616,7 @@
         <v>37</v>
       </c>
       <c r="J78" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -11588,7 +11648,7 @@
         <v>37</v>
       </c>
       <c r="J79" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -11620,7 +11680,7 @@
         <v>37</v>
       </c>
       <c r="J80" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -11652,7 +11712,7 @@
         <v>37</v>
       </c>
       <c r="J81" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -11684,7 +11744,7 @@
         <v>37</v>
       </c>
       <c r="J82" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -11716,7 +11776,7 @@
         <v>37</v>
       </c>
       <c r="J83" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -11748,7 +11808,7 @@
         <v>37</v>
       </c>
       <c r="J84" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -11780,7 +11840,7 @@
         <v>37</v>
       </c>
       <c r="J85" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -11812,7 +11872,7 @@
         <v>37</v>
       </c>
       <c r="J86" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -11844,7 +11904,7 @@
         <v>37</v>
       </c>
       <c r="J87" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -11876,7 +11936,7 @@
         <v>37</v>
       </c>
       <c r="J88" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -11908,7 +11968,7 @@
         <v>37</v>
       </c>
       <c r="J89" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -11940,7 +12000,7 @@
         <v>37</v>
       </c>
       <c r="J90" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -11972,7 +12032,7 @@
         <v>37</v>
       </c>
       <c r="J91" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -12004,7 +12064,7 @@
         <v>37</v>
       </c>
       <c r="J92" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -12036,7 +12096,7 @@
         <v>37</v>
       </c>
       <c r="J93" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -12068,7 +12128,7 @@
         <v>37</v>
       </c>
       <c r="J94" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -12100,7 +12160,7 @@
         <v>37</v>
       </c>
       <c r="J95" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -12132,7 +12192,7 @@
         <v>37</v>
       </c>
       <c r="J96" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -12164,7 +12224,7 @@
         <v>37</v>
       </c>
       <c r="J97" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -12196,7 +12256,7 @@
         <v>37</v>
       </c>
       <c r="J98" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -12228,7 +12288,7 @@
         <v>37</v>
       </c>
       <c r="J99" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -12260,7 +12320,7 @@
         <v>37</v>
       </c>
       <c r="J100" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -12292,7 +12352,7 @@
         <v>37</v>
       </c>
       <c r="J101" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -12324,7 +12384,7 @@
         <v>37</v>
       </c>
       <c r="J102" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -12356,7 +12416,7 @@
         <v>37</v>
       </c>
       <c r="J103" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -12388,7 +12448,7 @@
         <v>37</v>
       </c>
       <c r="J104" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -12420,7 +12480,7 @@
         <v>37</v>
       </c>
       <c r="J105" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -12452,7 +12512,7 @@
         <v>37</v>
       </c>
       <c r="J106" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -12484,7 +12544,7 @@
         <v>37</v>
       </c>
       <c r="J107" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -12516,7 +12576,7 @@
         <v>37</v>
       </c>
       <c r="J108" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -12548,7 +12608,7 @@
         <v>37</v>
       </c>
       <c r="J109" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -12580,7 +12640,7 @@
         <v>37</v>
       </c>
       <c r="J110" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -12612,7 +12672,7 @@
         <v>37</v>
       </c>
       <c r="J111" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -12644,7 +12704,7 @@
         <v>37</v>
       </c>
       <c r="J112" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -12676,7 +12736,7 @@
         <v>37</v>
       </c>
       <c r="J113" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -12708,7 +12768,7 @@
         <v>37</v>
       </c>
       <c r="J114" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -12740,7 +12800,7 @@
         <v>37</v>
       </c>
       <c r="J115" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -12772,7 +12832,7 @@
         <v>37</v>
       </c>
       <c r="J116" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -12804,7 +12864,7 @@
         <v>37</v>
       </c>
       <c r="J117" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -12836,7 +12896,7 @@
         <v>37</v>
       </c>
       <c r="J118" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -12868,7 +12928,7 @@
         <v>37</v>
       </c>
       <c r="J119" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -12900,7 +12960,7 @@
         <v>37</v>
       </c>
       <c r="J120" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -12932,7 +12992,7 @@
         <v>37</v>
       </c>
       <c r="J121" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -12964,7 +13024,7 @@
         <v>37</v>
       </c>
       <c r="J122" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -12996,7 +13056,7 @@
         <v>37</v>
       </c>
       <c r="J123" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -13028,7 +13088,7 @@
         <v>37</v>
       </c>
       <c r="J124" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -13060,7 +13120,7 @@
         <v>37</v>
       </c>
       <c r="J125" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -13092,7 +13152,7 @@
         <v>37</v>
       </c>
       <c r="J126" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -13124,7 +13184,7 @@
         <v>37</v>
       </c>
       <c r="J127" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -13156,7 +13216,7 @@
         <v>37</v>
       </c>
       <c r="J128" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -13188,7 +13248,7 @@
         <v>37</v>
       </c>
       <c r="J129" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -13220,7 +13280,7 @@
         <v>37</v>
       </c>
       <c r="J130" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -13252,7 +13312,7 @@
         <v>37</v>
       </c>
       <c r="J131" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -13284,7 +13344,7 @@
         <v>37</v>
       </c>
       <c r="J132" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -13316,7 +13376,7 @@
         <v>37</v>
       </c>
       <c r="J133" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -13348,7 +13408,7 @@
         <v>37</v>
       </c>
       <c r="J134" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -13380,7 +13440,7 @@
         <v>37</v>
       </c>
       <c r="J135" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -13412,7 +13472,7 @@
         <v>37</v>
       </c>
       <c r="J136" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -13444,7 +13504,7 @@
         <v>37</v>
       </c>
       <c r="J137" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -13476,7 +13536,7 @@
         <v>37</v>
       </c>
       <c r="J138" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -13508,7 +13568,7 @@
         <v>37</v>
       </c>
       <c r="J139" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -13540,7 +13600,7 @@
         <v>37</v>
       </c>
       <c r="J140" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -13572,7 +13632,7 @@
         <v>37</v>
       </c>
       <c r="J141" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -13604,7 +13664,7 @@
         <v>37</v>
       </c>
       <c r="J142" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -13636,7 +13696,7 @@
         <v>37</v>
       </c>
       <c r="J143" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -13668,7 +13728,7 @@
         <v>37</v>
       </c>
       <c r="J144" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -13700,7 +13760,7 @@
         <v>37</v>
       </c>
       <c r="J145" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -13732,7 +13792,7 @@
         <v>37</v>
       </c>
       <c r="J146" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -13764,7 +13824,7 @@
         <v>37</v>
       </c>
       <c r="J147" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -13796,7 +13856,7 @@
         <v>37</v>
       </c>
       <c r="J148" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -13828,7 +13888,7 @@
         <v>37</v>
       </c>
       <c r="J149" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -13860,7 +13920,7 @@
         <v>37</v>
       </c>
       <c r="J150" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -13892,7 +13952,7 @@
         <v>37</v>
       </c>
       <c r="J151" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -13924,7 +13984,7 @@
         <v>37</v>
       </c>
       <c r="J152" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -13956,7 +14016,7 @@
         <v>37</v>
       </c>
       <c r="J153" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -13988,7 +14048,7 @@
         <v>37</v>
       </c>
       <c r="J154" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -14020,7 +14080,7 @@
         <v>37</v>
       </c>
       <c r="J155" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -14052,7 +14112,7 @@
         <v>37</v>
       </c>
       <c r="J156" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -14084,7 +14144,7 @@
         <v>37</v>
       </c>
       <c r="J157" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -14116,7 +14176,7 @@
         <v>37</v>
       </c>
       <c r="J158" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -14148,7 +14208,7 @@
         <v>37</v>
       </c>
       <c r="J159" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -14180,7 +14240,7 @@
         <v>37</v>
       </c>
       <c r="J160" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -14212,7 +14272,7 @@
         <v>37</v>
       </c>
       <c r="J161" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -14244,7 +14304,7 @@
         <v>37</v>
       </c>
       <c r="J162" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -14276,7 +14336,7 @@
         <v>37</v>
       </c>
       <c r="J163" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -14308,7 +14368,7 @@
         <v>37</v>
       </c>
       <c r="J164" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -14340,7 +14400,7 @@
         <v>37</v>
       </c>
       <c r="J165" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -14372,7 +14432,7 @@
         <v>37</v>
       </c>
       <c r="J166" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -14404,7 +14464,7 @@
         <v>37</v>
       </c>
       <c r="J167" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -14436,7 +14496,7 @@
         <v>37</v>
       </c>
       <c r="J168" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -14468,7 +14528,7 @@
         <v>37</v>
       </c>
       <c r="J169" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -14500,7 +14560,7 @@
         <v>37</v>
       </c>
       <c r="J170" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -14532,7 +14592,7 @@
         <v>37</v>
       </c>
       <c r="J171" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -14564,7 +14624,7 @@
         <v>37</v>
       </c>
       <c r="J172" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -14596,7 +14656,7 @@
         <v>37</v>
       </c>
       <c r="J173" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -14628,7 +14688,7 @@
         <v>37</v>
       </c>
       <c r="J174" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -14660,7 +14720,7 @@
         <v>37</v>
       </c>
       <c r="J175" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -14692,7 +14752,7 @@
         <v>37</v>
       </c>
       <c r="J176" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -14724,7 +14784,7 @@
         <v>37</v>
       </c>
       <c r="J177" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -14756,7 +14816,7 @@
         <v>37</v>
       </c>
       <c r="J178" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -14788,7 +14848,7 @@
         <v>37</v>
       </c>
       <c r="J179" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -14820,7 +14880,7 @@
         <v>37</v>
       </c>
       <c r="J180" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -14852,7 +14912,7 @@
         <v>37</v>
       </c>
       <c r="J181" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -14884,7 +14944,7 @@
         <v>37</v>
       </c>
       <c r="J182" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -14916,7 +14976,7 @@
         <v>37</v>
       </c>
       <c r="J183" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -14948,7 +15008,7 @@
         <v>37</v>
       </c>
       <c r="J184" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -14980,7 +15040,7 @@
         <v>37</v>
       </c>
       <c r="J185" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -15012,7 +15072,7 @@
         <v>37</v>
       </c>
       <c r="J186" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -15044,7 +15104,7 @@
         <v>37</v>
       </c>
       <c r="J187" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -15076,7 +15136,7 @@
         <v>37</v>
       </c>
       <c r="J188" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -15108,7 +15168,7 @@
         <v>37</v>
       </c>
       <c r="J189" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -15140,7 +15200,7 @@
         <v>37</v>
       </c>
       <c r="J190" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -15172,7 +15232,7 @@
         <v>37</v>
       </c>
       <c r="J191" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -15204,7 +15264,7 @@
         <v>37</v>
       </c>
       <c r="J192" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -15236,7 +15296,7 @@
         <v>37</v>
       </c>
       <c r="J193" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -15268,7 +15328,7 @@
         <v>37</v>
       </c>
       <c r="J194" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -15300,7 +15360,7 @@
         <v>37</v>
       </c>
       <c r="J195" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -15332,7 +15392,7 @@
         <v>37</v>
       </c>
       <c r="J196" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -15364,7 +15424,7 @@
         <v>37</v>
       </c>
       <c r="J197" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -15396,7 +15456,7 @@
         <v>37</v>
       </c>
       <c r="J198" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -15428,7 +15488,7 @@
         <v>37</v>
       </c>
       <c r="J199" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -15460,7 +15520,7 @@
         <v>37</v>
       </c>
       <c r="J200" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -15492,7 +15552,7 @@
         <v>37</v>
       </c>
       <c r="J201" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -15524,7 +15584,7 @@
         <v>37</v>
       </c>
       <c r="J202" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -15556,7 +15616,7 @@
         <v>37</v>
       </c>
       <c r="J203" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -15588,7 +15648,7 @@
         <v>37</v>
       </c>
       <c r="J204" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -15620,7 +15680,7 @@
         <v>37</v>
       </c>
       <c r="J205" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -15652,7 +15712,7 @@
         <v>37</v>
       </c>
       <c r="J206" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -15684,7 +15744,7 @@
         <v>37</v>
       </c>
       <c r="J207" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -15716,7 +15776,7 @@
         <v>37</v>
       </c>
       <c r="J208" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -15748,7 +15808,7 @@
         <v>37</v>
       </c>
       <c r="J209" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -15780,7 +15840,7 @@
         <v>37</v>
       </c>
       <c r="J210" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -15812,7 +15872,7 @@
         <v>37</v>
       </c>
       <c r="J211" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -15844,7 +15904,7 @@
         <v>37</v>
       </c>
       <c r="J212" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -15876,7 +15936,7 @@
         <v>37</v>
       </c>
       <c r="J213" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -15908,7 +15968,7 @@
         <v>37</v>
       </c>
       <c r="J214" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -15940,7 +16000,7 @@
         <v>37</v>
       </c>
       <c r="J215" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -15972,7 +16032,7 @@
         <v>37</v>
       </c>
       <c r="J216" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -16004,7 +16064,7 @@
         <v>37</v>
       </c>
       <c r="J217" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -16036,7 +16096,7 @@
         <v>37</v>
       </c>
       <c r="J218" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -16068,7 +16128,7 @@
         <v>37</v>
       </c>
       <c r="J219" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -16100,7 +16160,7 @@
         <v>37</v>
       </c>
       <c r="J220" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -16132,7 +16192,7 @@
         <v>37</v>
       </c>
       <c r="J221" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -16164,7 +16224,7 @@
         <v>37</v>
       </c>
       <c r="J222" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -16196,7 +16256,7 @@
         <v>37</v>
       </c>
       <c r="J223" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -16228,7 +16288,7 @@
         <v>37</v>
       </c>
       <c r="J224" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -16260,7 +16320,7 @@
         <v>37</v>
       </c>
       <c r="J225" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -16292,7 +16352,7 @@
         <v>37</v>
       </c>
       <c r="J226" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -16307,19 +16367,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -16330,13 +16390,13 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -16347,13 +16407,13 @@
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16364,13 +16424,13 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -16381,13 +16441,13 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -16398,30 +16458,30 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
